--- a/cuadros/JUNIO/CASTAÑO.xlsx
+++ b/cuadros/JUNIO/CASTAÑO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,6 +702,76 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>ID_20260601121330</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ALIVENSA, S.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>36787</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FERNANDO CABRERA </t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NRO DE FACTURA ERRADO</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>INC_111944_0.png INC_111944_1.jpeg</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>ID_20260603111944</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/CASTAÑO.xlsx
+++ b/cuadros/JUNIO/CASTAÑO.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -57,7 +56,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -420,8 +419,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -489,11 +488,6 @@
           <t>FOTO_INCIDENCIA</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -559,11 +553,6 @@
           <t>INC_114252_0.jpeg INC_114252_1.jpeg</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>ID_20260601114252</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -629,11 +618,6 @@
           <t>INC_121117_0.jpeg INC_121117_1.jpeg</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>ID_20260601120953</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -699,11 +683,6 @@
           <t>INC_121330_0.jpeg INC_121330_1.jpeg</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>ID_20260601121330</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -767,11 +746,6 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>INC_111944_0.png INC_111944_1.jpeg</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>ID_20260603111944</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/CASTAÑO.xlsx
+++ b/cuadros/JUNIO/CASTAÑO.xlsx
@@ -419,8 +419,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
+  <cols>
+    <col width="29.84375" customWidth="1" min="12" max="12"/>
+    <col width="40.765625" customWidth="1" min="14" max="14"/>
+    <col width="63.3046875" customWidth="1" min="15" max="15"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -485,6 +490,11 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>FOTO_INCIDENCIA</t>
         </is>
       </c>
@@ -548,7 +558,7 @@
           <t>RECUPERACIÓN</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>INC_114252_0.jpeg INC_114252_1.jpeg</t>
         </is>
@@ -613,7 +623,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>INC_121117_0.jpeg INC_121117_1.jpeg</t>
         </is>
@@ -678,7 +688,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>INC_121330_0.jpeg INC_121330_1.jpeg</t>
         </is>
@@ -743,7 +753,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>INC_111944_0.png INC_111944_1.jpeg</t>
         </is>

--- a/cuadros/JUNIO/CASTAÑO.xlsx
+++ b/cuadros/JUNIO/CASTAÑO.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -25,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -36,6 +37,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
   </fills>
@@ -51,12 +58,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -419,13 +427,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
-  <cols>
-    <col width="29.84375" customWidth="1" min="12" max="12"/>
-    <col width="40.765625" customWidth="1" min="14" max="14"/>
-    <col width="63.3046875" customWidth="1" min="15" max="15"/>
-  </cols>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -756,6 +759,66 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>INC_111944_0.png INC_111944_1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>INVERSIONES LA PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>001215</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARCOS GARCIA </t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ID_20260604155334</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/CASTAÑO.xlsx
+++ b/cuadros/JUNIO/CASTAÑO.xlsx
@@ -26,24 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,10 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,7 +534,7 @@
           <t xml:space="preserve">ERROR AL CARGAR LA TARA SE COLOCO 2.8 KG Y EL PESO REAL DE CESTA ES DE 2.4 KG </t>
         </is>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="J2" t="n">
         <v>2.45</v>
       </c>
       <c r="K2" t="inlineStr">
@@ -561,6 +547,7 @@
           <t>RECUPERACIÓN</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>INC_114252_0.jpeg INC_114252_1.jpeg</t>
@@ -626,6 +613,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>INC_121117_0.jpeg INC_121117_1.jpeg</t>
@@ -691,6 +679,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>INC_121330_0.jpeg INC_121330_1.jpeg</t>
@@ -756,69 +745,10 @@
           <t>NINGUNA</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>INC_111944_0.png INC_111944_1.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CASTAÑO</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>INVERSIONES LA PATRONAS 2024, C.A.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>001215</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RECEPCION</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MARCOS GARCIA </t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>TIPO A</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>SIN_FOTO</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>COBRO</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>ID_20260604155334</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/CASTAÑO.xlsx
+++ b/cuadros/JUNIO/CASTAÑO.xlsx
@@ -26,12 +26,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +548,7 @@
           <t xml:space="preserve">ERROR AL CARGAR LA TARA SE COLOCO 2.8 KG Y EL PESO REAL DE CESTA ES DE 2.4 KG </t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="1" t="n">
         <v>2.45</v>
       </c>
       <c r="K2" t="inlineStr">
@@ -547,7 +561,6 @@
           <t>RECUPERACIÓN</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>INC_114252_0.jpeg INC_114252_1.jpeg</t>
@@ -613,7 +626,6 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>INC_121117_0.jpeg INC_121117_1.jpeg</t>
@@ -679,7 +691,6 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>INC_121330_0.jpeg INC_121330_1.jpeg</t>
@@ -745,10 +756,79 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>INC_111944_0.png INC_111944_1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>INVERSIONES LA PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>001215</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARCOS GARCIA </t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SE DETECTO UN FALTANTE EN EL PESAJE DE LA PATILLA DE 0.600 GR EL MISMO FUE CANCELADO POR LA SUCURSAL </t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>COB_160157_0.jpg</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ID_20260604160157</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>INC_160157_0.jpg INC_160157_1.jpeg</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/CASTAÑO.xlsx
+++ b/cuadros/JUNIO/CASTAÑO.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -829,6 +829,76 @@
       <c r="N6" t="inlineStr">
         <is>
           <t>INC_160157_0.jpg INC_160157_1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>INVERSIONES AJI, C.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>268102</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NEYDI JAZPE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>NRO DE CONTROL ERRADO</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ID_20260605100441</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>INC_100441_0.png INC_100441_1.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/CASTAÑO.xlsx
+++ b/cuadros/JUNIO/CASTAÑO.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,6 +899,76 @@
       <c r="N7" t="inlineStr">
         <is>
           <t>INC_100441_0.png INC_100441_1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MASSIVO CORPORATION, C.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>022982</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ANA BOLIVAR</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NRO DE CONTROL ERRADO</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ID_20260608114014</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>INC_114014_0.png INC_114014_1.jpeg</t>
         </is>
       </c>
     </row>
